--- a/templates_formats/Notas_Definitivas.xlsx
+++ b/templates_formats/Notas_Definitivas.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>Fecha:</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>Calif.</t>
-  </si>
-  <si>
-    <t>BIOLOGIA,  AMBIENTE  Y TECNOLOGIA</t>
   </si>
   <si>
     <t xml:space="preserve"> "NOMBRE PAIS "</t>
@@ -73,9 +70,24 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,16 +114,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="9"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="13"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -126,24 +135,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="15"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="16"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="18"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="19"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="15"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -156,11 +147,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="23"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,590 +472,620 @@
   <dimension ref="A1:Q69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.875" customWidth="1"/>
-    <col min="2" max="2" width="2" customWidth="1"/>
+    <col min="1" max="1" width="0.625" customWidth="1"/>
+    <col min="2" max="2" width="3" customWidth="1"/>
     <col min="3" max="3" width="18.5" customWidth="1"/>
-    <col min="4" max="4" width="4.75" customWidth="1"/>
+    <col min="4" max="4" width="4.375" customWidth="1"/>
     <col min="5" max="5" width="18.5" customWidth="1"/>
-    <col min="6" max="6" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.25" customWidth="1"/>
     <col min="7" max="7" width="18.5" customWidth="1"/>
-    <col min="8" max="8" width="5.125" customWidth="1"/>
+    <col min="8" max="8" width="4.25" customWidth="1"/>
     <col min="9" max="9" width="18.5" customWidth="1"/>
     <col min="10" max="10" width="4.25" customWidth="1"/>
     <col min="11" max="11" width="18.5" customWidth="1"/>
-    <col min="12" max="12" width="5" customWidth="1"/>
+    <col min="12" max="12" width="4.375" customWidth="1"/>
     <col min="13" max="15" width="2.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D1" s="19" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-    </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D2" s="11" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D3" s="10" t="s">
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D4" s="20" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D5" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="9"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+    </row>
+    <row r="6" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="3"/>
-      <c r="E6" s="2"/>
-      <c r="G6" s="1"/>
-      <c r="K6" s="8" t="s">
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D7" s="4"/>
+      <c r="E7" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="2"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="2"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D9" s="5"/>
-      <c r="G9" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="6"/>
-      <c r="C11" t="s">
+    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="5"/>
+      <c r="C11" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="5"/>
+      <c r="D11" s="4"/>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="16" t="s">
         <v>7</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="16" t="s">
         <v>8</v>
       </c>
       <c r="J11" s="1"/>
-      <c r="K11" t="s">
+      <c r="K11" s="13" t="s">
         <v>9</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="6"/>
-      <c r="C12" s="6" t="s">
+    <row r="12" spans="1:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="6"/>
-      <c r="C13" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
+    <row r="13" spans="1:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="6"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="16"/>
+    <row r="14" spans="1:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
+        <v>2</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="6"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="16"/>
+    <row r="15" spans="1:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="5">
+        <v>3</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="6"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
+    <row r="16" spans="1:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
+        <v>4</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="6"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="16"/>
+    <row r="17" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="5">
+        <v>5</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
+    <row r="18" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="5">
+        <v>6</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
     </row>
-    <row r="19" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="6"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
+    <row r="19" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="5">
+        <v>7</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="6"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
+    <row r="20" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="5">
+        <v>8</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
       <c r="P20" s="1"/>
     </row>
-    <row r="21" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="6"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="16"/>
+    <row r="21" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="5">
+        <v>9</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
       <c r="P21" s="1"/>
     </row>
-    <row r="22" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="6"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="16"/>
+    <row r="22" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="5">
+        <v>10</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
       <c r="P22" s="1"/>
     </row>
-    <row r="23" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
+    <row r="23" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="5">
+        <v>11</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
       <c r="P23" s="1"/>
     </row>
-    <row r="24" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="6"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
+    <row r="24" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="5">
+        <v>12</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
       <c r="P24" s="1"/>
     </row>
-    <row r="25" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="6"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
+    <row r="25" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="5">
+        <v>13</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
       <c r="P25" s="1"/>
     </row>
-    <row r="26" spans="2:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="6"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
+    <row r="26" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="5"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
       <c r="P26" s="1"/>
     </row>
-    <row r="27" spans="2:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="6"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-    </row>
-    <row r="28" spans="2:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="6"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-    </row>
-    <row r="29" spans="2:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-    </row>
-    <row r="30" spans="2:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-    </row>
-    <row r="31" spans="2:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-    </row>
-    <row r="32" spans="2:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-    </row>
-    <row r="33" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-    </row>
-    <row r="34" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="5"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+    </row>
+    <row r="28" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+    </row>
+    <row r="29" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+    </row>
+    <row r="30" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+    </row>
+    <row r="31" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+    </row>
+    <row r="32" spans="2:17" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="M32" s="10"/>
+    </row>
+    <row r="33" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="M33" s="10"/>
+    </row>
+    <row r="34" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
     </row>
-    <row r="35" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
     </row>
-    <row r="36" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
     </row>
-    <row r="37" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
     </row>
-    <row r="38" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
     </row>
-    <row r="39" spans="3:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
-    <row r="40" spans="3:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
-    <row r="41" spans="3:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
     </row>
-    <row r="42" spans="3:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
     </row>
-    <row r="43" spans="3:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
     </row>
-    <row r="44" spans="3:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
     </row>
-    <row r="45" spans="3:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" spans="3:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
     </row>
-    <row r="47" spans="3:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-    </row>
-    <row r="48" spans="3:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-    </row>
-    <row r="49" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
+    <row r="47" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:13" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
       <c r="P50" s="1"/>
     </row>
-    <row r="51" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
+    <row r="51" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
       <c r="P51" s="1"/>
     </row>
-    <row r="52" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -1057,105 +1093,105 @@
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
     </row>
-    <row r="53" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
     </row>
-    <row r="54" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
     </row>
-    <row r="55" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
       <c r="P55" s="1"/>
     </row>
-    <row r="56" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
       <c r="P56" s="1"/>
     </row>
-    <row r="57" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
       <c r="P57" s="1"/>
     </row>
-    <row r="58" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
     </row>
-    <row r="59" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
       <c r="P59" s="1"/>
     </row>
-    <row r="60" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
     </row>
-    <row r="61" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
       <c r="P61" s="1"/>
     </row>
-    <row r="62" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
     </row>
-    <row r="65" spans="12:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="12:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
       <c r="P65" s="1"/>
     </row>
-    <row r="66" spans="12:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="12:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
     </row>
-    <row r="67" spans="12:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="12:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
@@ -1177,6 +1213,14 @@
       <c r="P69" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A2:L2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="172" orientation="landscape" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
